--- a/backend/data/financials_by_company/0598.HK.xlsx
+++ b/backend/data/financials_by_company/0598.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB5"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,646 +692,704 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>66569950.150211</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.167044</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4994004430.4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>423849231.89</v>
-      </c>
-      <c r="F2" t="n">
-        <v>398516707.8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3917651361.38</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>2474463188.31</v>
-      </c>
-      <c r="I2" t="n">
-        <v>103773712413.46</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5417853662.29</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5417853662.29</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-307622897.18</v>
-      </c>
-      <c r="M2" t="n">
-        <v>400003767.71</v>
-      </c>
-      <c r="N2" t="n">
-        <v>141358846.67</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3611037127.820211</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3917651361.38</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>102666470050.21</v>
-      </c>
-      <c r="R2" t="n">
-        <v>56837862.09</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4939813493.69</v>
-      </c>
+        <v>2101376039.79</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>7273767845</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>3917651361.38</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3917651361.38</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3917651361.38</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-261995238.82</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4179646600.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4179646600.2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>838203294.38</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5017849894.58</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>33345513.2</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>109780645.13</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-107177346.94</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>85479251.25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-113415073.53</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-307622897.18</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>48977976.14</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>400003767.71</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>141358846.67</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2954303305.22</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-1107242363.25</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>329597143.82</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>120658190.73</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>618722657.03</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>137861360.88</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>480861296.15</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>1847060941.97</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>103773712413.46</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>105620773355.43</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>105620773355.43</v>
-      </c>
+        <v>7400803875</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7400803875</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>51974828.04</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>25256802.582459</v>
+        <v>17083851.074066</v>
       </c>
       <c r="C3" t="n">
-        <v>0.19181</v>
+        <v>0.184522</v>
       </c>
       <c r="D3" t="n">
-        <v>5562062119.62</v>
+        <v>5630949847.36</v>
       </c>
       <c r="E3" t="n">
-        <v>458230073.26</v>
+        <v>92584315.31</v>
       </c>
       <c r="F3" t="n">
-        <v>131676287.76</v>
+        <v>92584315.31</v>
       </c>
       <c r="G3" t="n">
-        <v>4214787238.59</v>
+        <v>4079192956.09</v>
       </c>
       <c r="H3" t="n">
-        <v>2464068269.76</v>
+        <v>2310098291.24</v>
       </c>
       <c r="I3" t="n">
-        <v>99681873242.28</v>
+        <v>106938385095.05</v>
       </c>
       <c r="J3" t="n">
-        <v>6020292192.88</v>
+        <v>5723534162.67</v>
       </c>
       <c r="K3" t="n">
-        <v>6020292192.88</v>
+        <v>5723534162.67</v>
       </c>
       <c r="L3" t="n">
-        <v>-277251552.28</v>
+        <v>-328526569.15</v>
       </c>
       <c r="M3" t="n">
-        <v>519566444.65</v>
+        <v>480048437.63</v>
       </c>
       <c r="N3" t="n">
-        <v>277907186.18</v>
+        <v>180952727.67</v>
       </c>
       <c r="O3" t="n">
-        <v>4434921538.912459</v>
+        <v>4003692491.854066</v>
       </c>
       <c r="P3" t="n">
-        <v>4214787238.59</v>
+        <v>4079192956.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>98455572223.7</v>
+        <v>106602541296.31</v>
       </c>
       <c r="R3" t="n">
-        <v>58379985.8</v>
+        <v>61359809.98</v>
       </c>
       <c r="S3" t="n">
-        <v>5463894585.42</v>
+        <v>5247925826.48</v>
       </c>
       <c r="T3" t="n">
-        <v>7251532966</v>
+        <v>7350859817</v>
       </c>
       <c r="U3" t="n">
-        <v>7245419625</v>
+        <v>7350859817</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5812</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5817</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4214787238.59</v>
+        <v>4079192956.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>4214787238.59</v>
+        <v>4079192956.09</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>4214787238.59</v>
+        <v>4079192956.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>-230845397.23</v>
+        <v>-196753840.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>4445632635.82</v>
+        <v>4275946796.49</v>
       </c>
       <c r="AD3" t="n">
-        <v>4445632635.82</v>
+        <v>4275946796.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>1055093112.41</v>
+        <v>967538928.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>5500725748.23</v>
+        <v>5243485725.04</v>
       </c>
       <c r="AG3" t="n">
-        <v>49198184.08</v>
+        <v>22397312</v>
       </c>
       <c r="AH3" t="n">
-        <v>-191756330.83</v>
+        <v>21988292.86</v>
       </c>
       <c r="AI3" t="n">
-        <v>-159998545.32</v>
+        <v>-148324295.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24937609.5</v>
+        <v>27889339.77</v>
       </c>
       <c r="AK3" t="n">
-        <v>394810.44</v>
+        <v>116115432.22</v>
       </c>
       <c r="AL3" t="n">
-        <v>-131329.29</v>
+        <v>-17668769.65</v>
       </c>
       <c r="AM3" t="n">
-        <v>-277251552.28</v>
+        <v>-328526569.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>35592293.81</v>
+        <v>29430859.19</v>
       </c>
       <c r="AO3" t="n">
-        <v>519566444.65</v>
+        <v>480048437.63</v>
       </c>
       <c r="AP3" t="n">
-        <v>277907186.18</v>
+        <v>180952727.67</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3309080315.1</v>
+        <v>2690959633.06</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1226301018.58</v>
+        <v>-335843798.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>191542505.05</v>
+        <v>152688672.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>233188701.16</v>
+        <v>196139497.55</v>
       </c>
       <c r="AU3" t="n">
-        <v>704675176.1</v>
+        <v>689523770.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>165127725.04</v>
+        <v>136084328.54</v>
       </c>
       <c r="AW3" t="n">
-        <v>539547451.0599999</v>
+        <v>553439441.71</v>
       </c>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>2082779296.52</v>
+        <v>2355115834.32</v>
       </c>
       <c r="AZ3" t="n">
-        <v>99681873242.28</v>
+        <v>106938385095.05</v>
       </c>
       <c r="BA3" t="n">
-        <v>101764652538.8</v>
+        <v>109293500929.37</v>
       </c>
       <c r="BB3" t="n">
-        <v>101764652538.8</v>
+        <v>109293500929.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>17083851.074066</v>
+        <v>25256802.582459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.184522</v>
+        <v>0.19181</v>
       </c>
       <c r="D4" t="n">
-        <v>5630949847.36</v>
+        <v>5562062119.62</v>
       </c>
       <c r="E4" t="n">
-        <v>92584315.31</v>
+        <v>458230073.26</v>
       </c>
       <c r="F4" t="n">
-        <v>92584315.31</v>
+        <v>131676287.76</v>
       </c>
       <c r="G4" t="n">
-        <v>4079192956.09</v>
+        <v>4214787238.59</v>
       </c>
       <c r="H4" t="n">
-        <v>2310098291.24</v>
+        <v>2464068269.76</v>
       </c>
       <c r="I4" t="n">
-        <v>106938385095.05</v>
+        <v>99681873242.28</v>
       </c>
       <c r="J4" t="n">
-        <v>5723534162.67</v>
+        <v>6020292192.88</v>
       </c>
       <c r="K4" t="n">
-        <v>5723534162.67</v>
+        <v>6020292192.88</v>
       </c>
       <c r="L4" t="n">
-        <v>-328526569.15</v>
+        <v>-277251552.28</v>
       </c>
       <c r="M4" t="n">
-        <v>480048437.63</v>
+        <v>519566444.65</v>
       </c>
       <c r="N4" t="n">
-        <v>180952727.67</v>
+        <v>277907186.18</v>
       </c>
       <c r="O4" t="n">
-        <v>4003692491.854066</v>
+        <v>4434921538.912459</v>
       </c>
       <c r="P4" t="n">
-        <v>4079192956.09</v>
+        <v>4214787238.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>106602541296.31</v>
+        <v>98455572223.7</v>
       </c>
       <c r="R4" t="n">
-        <v>61359809.98</v>
+        <v>58379985.8</v>
       </c>
       <c r="S4" t="n">
-        <v>5247925826.48</v>
+        <v>5463894585.42</v>
       </c>
       <c r="T4" t="n">
-        <v>7350859817</v>
+        <v>7251532966</v>
       </c>
       <c r="U4" t="n">
-        <v>7350859817</v>
+        <v>7245419625</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5812</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5817</v>
       </c>
       <c r="X4" t="n">
-        <v>4079192956.09</v>
+        <v>4214787238.59</v>
       </c>
       <c r="Y4" t="n">
-        <v>4079192956.09</v>
+        <v>4214787238.59</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4079192956.09</v>
+        <v>4214787238.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>-196753840.4</v>
+        <v>-230845397.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>4275946796.49</v>
+        <v>4445632635.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>4275946796.49</v>
+        <v>4445632635.82</v>
       </c>
       <c r="AE4" t="n">
-        <v>967538928.55</v>
+        <v>1055093112.41</v>
       </c>
       <c r="AF4" t="n">
-        <v>5243485725.04</v>
+        <v>5500725748.23</v>
       </c>
       <c r="AG4" t="n">
-        <v>22397312</v>
+        <v>49198184.08</v>
       </c>
       <c r="AH4" t="n">
-        <v>21988292.86</v>
+        <v>-191756330.83</v>
       </c>
       <c r="AI4" t="n">
-        <v>-148324295.2</v>
+        <v>-159998545.32</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27889339.77</v>
+        <v>24937609.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>116115432.22</v>
+        <v>394810.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>-17668769.65</v>
+        <v>-131329.29</v>
       </c>
       <c r="AM4" t="n">
-        <v>-328526569.15</v>
+        <v>-277251552.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>29430859.19</v>
+        <v>35592293.81</v>
       </c>
       <c r="AO4" t="n">
-        <v>480048437.63</v>
+        <v>519566444.65</v>
       </c>
       <c r="AP4" t="n">
-        <v>180952727.67</v>
+        <v>277907186.18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2690959633.06</v>
+        <v>3309080315.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>-335843798.74</v>
+        <v>-1226301018.58</v>
       </c>
       <c r="AS4" t="n">
-        <v>152688672.92</v>
+        <v>191542505.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>196139497.55</v>
+        <v>233188701.16</v>
       </c>
       <c r="AU4" t="n">
-        <v>689523770.25</v>
+        <v>704675176.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>136084328.54</v>
+        <v>165127725.04</v>
       </c>
       <c r="AW4" t="n">
-        <v>553439441.71</v>
+        <v>539547451.0599999</v>
       </c>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>2355115834.32</v>
+        <v>2082779296.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>106938385095.05</v>
+        <v>99681873242.28</v>
       </c>
       <c r="BA4" t="n">
-        <v>109293500929.37</v>
+        <v>101764652538.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>109293500929.37</v>
+        <v>101764652538.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-60999046.941786</v>
+        <v>66569950.150211</v>
       </c>
       <c r="C5" t="n">
-        <v>0.168955</v>
+        <v>0.167044</v>
       </c>
       <c r="D5" t="n">
-        <v>5430494791.88</v>
+        <v>4994004430.4</v>
       </c>
       <c r="E5" t="n">
-        <v>-281416036.35</v>
+        <v>423849231.89</v>
       </c>
       <c r="F5" t="n">
-        <v>-361037607.08</v>
+        <v>398516707.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3713520003.28</v>
+        <v>3917651361.38</v>
       </c>
       <c r="H5" t="n">
-        <v>2101376039.79</v>
+        <v>2474463188.31</v>
       </c>
       <c r="I5" t="n">
-        <v>121311342360.39</v>
+        <v>103773712413.46</v>
       </c>
       <c r="J5" t="n">
-        <v>5149078755.53</v>
+        <v>5417853662.29</v>
       </c>
       <c r="K5" t="n">
-        <v>5149078755.53</v>
+        <v>5417853662.29</v>
       </c>
       <c r="L5" t="n">
-        <v>-292539944.65</v>
+        <v>-307622897.18</v>
       </c>
       <c r="M5" t="n">
-        <v>416678883.97</v>
+        <v>400003767.71</v>
       </c>
       <c r="N5" t="n">
-        <v>138339997.11</v>
+        <v>141358846.67</v>
       </c>
       <c r="O5" t="n">
-        <v>4093180134.148214</v>
+        <v>3611037127.820211</v>
       </c>
       <c r="P5" t="n">
-        <v>3713520003.28</v>
+        <v>3917651361.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>121294265788.99</v>
+        <v>102666470050.21</v>
       </c>
       <c r="R5" t="n">
-        <v>38432228.4</v>
+        <v>56837862.09</v>
       </c>
       <c r="S5" t="n">
-        <v>4867406966.46</v>
+        <v>4939813493.69</v>
       </c>
       <c r="T5" t="n">
-        <v>7400803875</v>
-      </c>
-      <c r="U5" t="n">
-        <v>7400803875</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.5</v>
-      </c>
+        <v>7273767845</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>3713520003.28</v>
+        <v>3917651361.38</v>
       </c>
       <c r="Y5" t="n">
-        <v>3713520003.28</v>
+        <v>3917651361.38</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3713520003.28</v>
+        <v>3917651361.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>-219318060.17</v>
+        <v>-261995238.82</v>
       </c>
       <c r="AC5" t="n">
-        <v>3932838063.45</v>
+        <v>4179646600.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>3932838063.45</v>
+        <v>4179646600.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>799561808.11</v>
+        <v>838203294.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>4732399871.56</v>
+        <v>5017849894.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>28051264.67</v>
+        <v>33345513.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>-392070278.24</v>
+        <v>109780645.13</v>
       </c>
       <c r="AI5" t="n">
-        <v>73468069.62</v>
+        <v>-107177346.94</v>
       </c>
       <c r="AJ5" t="n">
-        <v>130566378.34</v>
+        <v>85479251.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>139441800.87</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-31027541.32</v>
+        <v>-113415073.53</v>
       </c>
       <c r="AM5" t="n">
-        <v>-292539944.65</v>
+        <v>-307622897.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>14201057.79</v>
+        <v>48977976.14</v>
       </c>
       <c r="AO5" t="n">
-        <v>416678883.97</v>
+        <v>400003767.71</v>
       </c>
       <c r="AP5" t="n">
-        <v>138339997.11</v>
+        <v>141358846.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3054128789.4</v>
+        <v>2954303305.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>-17076571.4</v>
+        <v>-1107242363.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>136962962.4</v>
+        <v>329597143.82</v>
       </c>
       <c r="AT5" t="n">
-        <v>171595536.54</v>
+        <v>120658190.73</v>
       </c>
       <c r="AU5" t="n">
-        <v>1509020141.49</v>
+        <v>618722657.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>973490694.74</v>
+        <v>137861360.88</v>
       </c>
       <c r="AW5" t="n">
-        <v>535529446.75</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>51974828.04</v>
-      </c>
+        <v>480861296.15</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>3037052218</v>
+        <v>1847060941.97</v>
       </c>
       <c r="AZ5" t="n">
-        <v>121311342360.39</v>
+        <v>103773712413.46</v>
       </c>
       <c r="BA5" t="n">
-        <v>124348394578.39</v>
+        <v>105620773355.43</v>
       </c>
       <c r="BB5" t="n">
-        <v>124348394578.39</v>
+        <v>105620773355.43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>188702311.429346</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.162494</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3722648039.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1722502130.58</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1161289127.55</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4021797495.79</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>94924183912.86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5445150169.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5445150169.88</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-217567770.66</v>
+      </c>
+      <c r="M6" t="n">
+        <v>330856180.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>158463510.85</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3610423682.699346</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4021797495.79</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>94173378308.81</v>
+      </c>
+      <c r="R6" t="n">
+        <v>58496283.14</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5157607331.33</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>4021797495.79</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4021797495.79</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4021797495.79</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-261455305.17</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4283252800.96</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4283252800.96</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>831041188.9</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>5114293989.86</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16480158.81</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-593458605.5599999</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-391225202.65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>388870953.34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>104591898.13</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-69992046.29000001</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-217567770.66</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>45175101.49</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>330856180.02</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>158463510.85</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2635285528.39</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-750805604.05</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>337714334.94</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>178977991.16</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>583792528.39</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>129167344.28</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>454625184.11</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>1884479924.34</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>94924183912.86</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>96808663837.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>96808663837.2</v>
       </c>
     </row>
   </sheetData>
@@ -1345,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA5"/>
+  <dimension ref="A1:CA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1742,940 +1800,1029 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>41327657</v>
-      </c>
-      <c r="C2" t="n">
-        <v>7252889218</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7294216875</v>
-      </c>
-      <c r="E2" t="n">
-        <v>11757656080.87</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31033280918.54</v>
-      </c>
-      <c r="G2" t="n">
-        <v>48593502362.83</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8707701345.049999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31033280918.54</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2731748480.34</v>
-      </c>
-      <c r="K2" t="n">
-        <v>39567594762.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>44874798628.22</v>
-      </c>
-      <c r="M2" t="n">
-        <v>42040678218.49</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2473083456.19</v>
-      </c>
-      <c r="O2" t="n">
-        <v>39567594762.3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>174944256.65</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>23424281261.35</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7294216875</v>
-      </c>
-      <c r="S2" t="n">
-        <v>7294216875</v>
-      </c>
-      <c r="T2" t="n">
-        <v>35154821919.36</v>
-      </c>
-      <c r="U2" t="n">
-        <v>8227525622.66</v>
-      </c>
-      <c r="V2" t="n">
-        <v>23339731.15</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>3564107.17</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>525236135.58</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>283733107.86</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7391652540.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2084448674.98</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5307203865.92</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>26927296296.7</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>10825386.94</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4366003539.97</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>647299805.36</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3718703734.61</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>174384897.33</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>15667557383.77</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1972767130.13</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>73788729.28</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>864106652.46</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>12756894871.9</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>77195500137.85001</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>41560502496.1</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>221218439.51</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>320385056.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1632133803.25</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>2579073.52</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>324454648.11</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>416867662.27</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1215266140.98</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9239887191.07</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2793232058.42</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>8534313843.76</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6568744342.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1965569500.96</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>18733510730.62</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-13792337643.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>32525848374.42</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>707241506.88</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>46402685.29</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>11155649758.93</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>20616554423.32</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>35634997641.75</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>3739850.11</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1378252249.97</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5533635740.3</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>56259409.64</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>7559958</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>48699451.64</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1820249334.4</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>322821726.49</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>13051800450.54</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>-545188204.76</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>13596988655.3</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>13468238880.3</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>574374.3199999999</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>13467664505.98</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>5787029280.41</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>7680635225.57</v>
-      </c>
+        <v>582917064.75</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>193951597</v>
+        <v>98582000</v>
       </c>
       <c r="C3" t="n">
-        <v>7100265278</v>
+        <v>7256522875</v>
       </c>
       <c r="D3" t="n">
-        <v>7294216875</v>
+        <v>7355104875</v>
       </c>
       <c r="E3" t="n">
-        <v>12661159546.27</v>
+        <v>15627724917.78</v>
       </c>
       <c r="F3" t="n">
-        <v>29163013753.44</v>
+        <v>26161734589.83</v>
       </c>
       <c r="G3" t="n">
-        <v>47309919239.71</v>
+        <v>47370743143</v>
       </c>
       <c r="H3" t="n">
-        <v>6581005556.37</v>
+        <v>10122662814.44</v>
       </c>
       <c r="I3" t="n">
-        <v>29163013753.44</v>
+        <v>26161734589.83</v>
       </c>
       <c r="J3" t="n">
-        <v>3155046277.23</v>
+        <v>3061413515.37</v>
       </c>
       <c r="K3" t="n">
-        <v>37803805970.67</v>
+        <v>34804431740.59</v>
       </c>
       <c r="L3" t="n">
-        <v>42158194509.78</v>
+        <v>44149839146.86</v>
       </c>
       <c r="M3" t="n">
-        <v>40121361569.35</v>
+        <v>36929705851.74</v>
       </c>
       <c r="N3" t="n">
-        <v>2317555598.68</v>
+        <v>2125274111.15</v>
       </c>
       <c r="O3" t="n">
-        <v>37803805970.67</v>
+        <v>34804431740.59</v>
       </c>
       <c r="P3" t="n">
-        <v>193951597</v>
+        <v>300752201.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>21890625834.25</v>
+        <v>19811097472.17</v>
       </c>
       <c r="R3" t="n">
-        <v>7294216875</v>
+        <v>7355104875</v>
       </c>
       <c r="S3" t="n">
-        <v>7294216875</v>
+        <v>7355104875</v>
       </c>
       <c r="T3" t="n">
-        <v>35785429845.01</v>
+        <v>41572733686.39</v>
       </c>
       <c r="U3" t="n">
-        <v>7729890229.78</v>
+        <v>12930392772.09</v>
       </c>
       <c r="V3" t="n">
-        <v>204512515.2</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>405193661.37</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2519966.86</v>
+      </c>
       <c r="X3" t="n">
-        <v>28077603.6</v>
+        <v>168794554.82</v>
       </c>
       <c r="Y3" t="n">
-        <v>406187032.26</v>
+        <v>412166773.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>238991734.02</v>
+        <v>193835071.39</v>
       </c>
       <c r="AA3" t="n">
-        <v>6852121344.7</v>
+        <v>11750402711.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>2497732805.59</v>
+        <v>2404995304.96</v>
       </c>
       <c r="AC3" t="n">
-        <v>4354388539.11</v>
+        <v>9345407406.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>28055539615.23</v>
+        <v>28642340914.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>27270020.42</v>
+        <v>3526967269.26</v>
       </c>
       <c r="AF3" t="n">
-        <v>5809038201.57</v>
+        <v>3877322206.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>657313471.64</v>
+        <v>656418210.41</v>
       </c>
       <c r="AH3" t="n">
-        <v>5151724729.93</v>
+        <v>3220903996.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>167702988.8</v>
+        <v>2296796648.54</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15598414441.92</v>
+        <v>18165740312.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>2353588008.22</v>
+        <v>3271150096.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>69477271.8</v>
+        <v>94429787.93000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>803564795.86</v>
+        <v>789336224.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>12371784366.04</v>
+        <v>14010824203.49</v>
       </c>
       <c r="AO3" t="n">
-        <v>75906791414.36</v>
+        <v>78502439538.13</v>
       </c>
       <c r="AP3" t="n">
-        <v>41270246242.76</v>
+        <v>39737435809.39</v>
       </c>
       <c r="AQ3" t="n">
-        <v>111764602.55</v>
+        <v>319998598.72</v>
       </c>
       <c r="AR3" t="n">
-        <v>248929133.7</v>
+        <v>254895122.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>277082418.64</v>
+        <v>252807288.97</v>
       </c>
       <c r="AT3" t="n">
-        <v>1392064537.28</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>775489534.74</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>36495000</v>
+      </c>
       <c r="AV3" t="n">
-        <v>415223441.98</v>
+        <v>30576728.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>976841095.3</v>
+        <v>708417806.54</v>
       </c>
       <c r="AX3" t="n">
-        <v>9137465343.85</v>
+        <v>8530841465.16</v>
       </c>
       <c r="AY3" t="n">
-        <v>2885653066.58</v>
+        <v>2273458834.63</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8640792217.23</v>
+        <v>8642697150.76</v>
       </c>
       <c r="BA3" t="n">
-        <v>6599243817.15</v>
+        <v>6434684627.52</v>
       </c>
       <c r="BB3" t="n">
-        <v>2041548400.08</v>
+        <v>2208012523.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>18576494922.93</v>
+        <v>18687247813.58</v>
       </c>
       <c r="BD3" t="n">
-        <v>-12884039149.41</v>
+        <v>-11882354334.55</v>
       </c>
       <c r="BE3" t="n">
-        <v>31460534072.34</v>
+        <v>30569602148.13</v>
       </c>
       <c r="BF3" t="n">
-        <v>863223325.24</v>
+        <v>846936770.37</v>
       </c>
       <c r="BG3" t="n">
-        <v>42767071.53</v>
+        <v>39560461.08</v>
       </c>
       <c r="BH3" t="n">
-        <v>10820595879.74</v>
+        <v>10582126092.54</v>
       </c>
       <c r="BI3" t="n">
-        <v>19733947795.83</v>
+        <v>19100978824.14</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>34636545171.6</v>
+        <v>38765003728.74</v>
       </c>
       <c r="BL3" t="n">
-        <v>13451969.09</v>
+        <v>440541486.22</v>
       </c>
       <c r="BM3" t="n">
-        <v>1345557994.59</v>
+        <v>1141178562.33</v>
       </c>
       <c r="BN3" t="n">
-        <v>5000914412.87</v>
+        <v>5971199489.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>58682194.17</v>
+        <v>74334275.04000001</v>
       </c>
       <c r="BP3" t="n">
-        <v>8795312.74</v>
+        <v>18893842.91</v>
       </c>
       <c r="BQ3" t="n">
-        <v>49886881.43</v>
+        <v>55440432.13</v>
       </c>
       <c r="BR3" t="n">
-        <v>1575715558.03</v>
+        <v>1246178202.49</v>
       </c>
       <c r="BS3" t="n">
-        <v>338502984.73</v>
+        <v>378538655.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>12334182715.65</v>
+        <v>13413688264.84</v>
       </c>
       <c r="BU3" t="n">
-        <v>-548601373.99</v>
+        <v>-551139675.42</v>
       </c>
       <c r="BV3" t="n">
-        <v>12882784089.64</v>
+        <v>13964827940.26</v>
       </c>
       <c r="BW3" t="n">
-        <v>13969537342.47</v>
+        <v>16539886278.81</v>
       </c>
       <c r="BX3" t="n">
-        <v>520189.78</v>
+        <v>664096.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>13969017152.69</v>
+        <v>16539222182.14</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4223397105.18</v>
+        <v>4710689120.03</v>
       </c>
       <c r="CA3" t="n">
-        <v>9745620047.51</v>
+        <v>11828533062.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>98582000</v>
+        <v>193951597</v>
       </c>
       <c r="C4" t="n">
-        <v>7256522875</v>
+        <v>7100265278</v>
       </c>
       <c r="D4" t="n">
-        <v>7355104875</v>
+        <v>7294216875</v>
       </c>
       <c r="E4" t="n">
-        <v>15627724917.78</v>
+        <v>12661159546.27</v>
       </c>
       <c r="F4" t="n">
-        <v>26161734589.83</v>
+        <v>29163013753.44</v>
       </c>
       <c r="G4" t="n">
-        <v>47370743143</v>
+        <v>47309919239.71</v>
       </c>
       <c r="H4" t="n">
-        <v>10122662814.44</v>
+        <v>6581005556.37</v>
       </c>
       <c r="I4" t="n">
-        <v>26161734589.83</v>
+        <v>29163013753.44</v>
       </c>
       <c r="J4" t="n">
-        <v>3061413515.37</v>
+        <v>3155046277.23</v>
       </c>
       <c r="K4" t="n">
-        <v>34804431740.59</v>
+        <v>37803805970.67</v>
       </c>
       <c r="L4" t="n">
-        <v>44149839146.86</v>
+        <v>42158194509.78</v>
       </c>
       <c r="M4" t="n">
-        <v>36929705851.74</v>
+        <v>40121361569.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2125274111.15</v>
+        <v>2317555598.68</v>
       </c>
       <c r="O4" t="n">
-        <v>34804431740.59</v>
+        <v>37803805970.67</v>
       </c>
       <c r="P4" t="n">
-        <v>300752201.55</v>
+        <v>193951597</v>
       </c>
       <c r="Q4" t="n">
-        <v>19811097472.17</v>
+        <v>21890625834.25</v>
       </c>
       <c r="R4" t="n">
-        <v>7355104875</v>
+        <v>7294216875</v>
       </c>
       <c r="S4" t="n">
-        <v>7355104875</v>
+        <v>7294216875</v>
       </c>
       <c r="T4" t="n">
-        <v>41572733686.39</v>
+        <v>35785429845.01</v>
       </c>
       <c r="U4" t="n">
-        <v>12930392772.09</v>
+        <v>7729890229.78</v>
       </c>
       <c r="V4" t="n">
-        <v>405193661.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2519966.86</v>
-      </c>
+        <v>204512515.2</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>168794554.82</v>
+        <v>28077603.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>412166773.28</v>
+        <v>406187032.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>193835071.39</v>
+        <v>238991734.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>11750402711.23</v>
+        <v>6852121344.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2404995304.96</v>
+        <v>2497732805.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>9345407406.27</v>
+        <v>4354388539.11</v>
       </c>
       <c r="AD4" t="n">
-        <v>28642340914.3</v>
+        <v>28055539615.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>3526967269.26</v>
+        <v>27270020.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>3877322206.55</v>
+        <v>5809038201.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>656418210.41</v>
+        <v>657313471.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>3220903996.14</v>
+        <v>5151724729.93</v>
       </c>
       <c r="AI4" t="n">
-        <v>2296796648.54</v>
+        <v>167702988.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18165740312.16</v>
+        <v>15598414441.92</v>
       </c>
       <c r="AK4" t="n">
-        <v>3271150096.58</v>
+        <v>2353588008.22</v>
       </c>
       <c r="AL4" t="n">
-        <v>94429787.93000001</v>
+        <v>69477271.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>789336224.16</v>
+        <v>803564795.86</v>
       </c>
       <c r="AN4" t="n">
-        <v>14010824203.49</v>
+        <v>12371784366.04</v>
       </c>
       <c r="AO4" t="n">
-        <v>78502439538.13</v>
+        <v>75906791414.36</v>
       </c>
       <c r="AP4" t="n">
-        <v>39737435809.39</v>
+        <v>41270246242.76</v>
       </c>
       <c r="AQ4" t="n">
-        <v>319998598.72</v>
+        <v>111764602.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>254895122.83</v>
+        <v>248929133.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>252807288.97</v>
+        <v>277082418.64</v>
       </c>
       <c r="AT4" t="n">
-        <v>775489534.74</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>36495000</v>
-      </c>
+        <v>1392064537.28</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>30576728.2</v>
+        <v>415223441.98</v>
       </c>
       <c r="AW4" t="n">
-        <v>708417806.54</v>
+        <v>976841095.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>8530841465.16</v>
+        <v>9137465343.85</v>
       </c>
       <c r="AY4" t="n">
-        <v>2273458834.63</v>
+        <v>2885653066.58</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8642697150.76</v>
+        <v>8640792217.23</v>
       </c>
       <c r="BA4" t="n">
-        <v>6434684627.52</v>
+        <v>6599243817.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>2208012523.24</v>
+        <v>2041548400.08</v>
       </c>
       <c r="BC4" t="n">
-        <v>18687247813.58</v>
+        <v>18576494922.93</v>
       </c>
       <c r="BD4" t="n">
-        <v>-11882354334.55</v>
+        <v>-12884039149.41</v>
       </c>
       <c r="BE4" t="n">
-        <v>30569602148.13</v>
+        <v>31460534072.34</v>
       </c>
       <c r="BF4" t="n">
-        <v>846936770.37</v>
+        <v>863223325.24</v>
       </c>
       <c r="BG4" t="n">
-        <v>39560461.08</v>
+        <v>42767071.53</v>
       </c>
       <c r="BH4" t="n">
-        <v>10582126092.54</v>
+        <v>10820595879.74</v>
       </c>
       <c r="BI4" t="n">
-        <v>19100978824.14</v>
+        <v>19733947795.83</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>38765003728.74</v>
+        <v>34636545171.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>440541486.22</v>
+        <v>13451969.09</v>
       </c>
       <c r="BM4" t="n">
-        <v>1141178562.33</v>
+        <v>1345557994.59</v>
       </c>
       <c r="BN4" t="n">
-        <v>5971199489.9</v>
+        <v>5000914412.87</v>
       </c>
       <c r="BO4" t="n">
-        <v>74334275.04000001</v>
+        <v>58682194.17</v>
       </c>
       <c r="BP4" t="n">
-        <v>18893842.91</v>
+        <v>8795312.74</v>
       </c>
       <c r="BQ4" t="n">
-        <v>55440432.13</v>
+        <v>49886881.43</v>
       </c>
       <c r="BR4" t="n">
-        <v>1246178202.49</v>
+        <v>1575715558.03</v>
       </c>
       <c r="BS4" t="n">
-        <v>378538655.33</v>
+        <v>338502984.73</v>
       </c>
       <c r="BT4" t="n">
-        <v>13413688264.84</v>
+        <v>12334182715.65</v>
       </c>
       <c r="BU4" t="n">
-        <v>-551139675.42</v>
+        <v>-548601373.99</v>
       </c>
       <c r="BV4" t="n">
-        <v>13964827940.26</v>
+        <v>12882784089.64</v>
       </c>
       <c r="BW4" t="n">
-        <v>16539886278.81</v>
+        <v>13969537342.47</v>
       </c>
       <c r="BX4" t="n">
-        <v>664096.67</v>
+        <v>520189.78</v>
       </c>
       <c r="BY4" t="n">
-        <v>16539222182.14</v>
+        <v>13969017152.69</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4710689120.03</v>
+        <v>4223397105.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>11828533062.11</v>
+        <v>9745620047.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>41327657</v>
+      </c>
       <c r="C5" t="n">
-        <v>7400803875</v>
+        <v>7252889218</v>
       </c>
       <c r="D5" t="n">
-        <v>7400803875</v>
+        <v>7294216875</v>
       </c>
       <c r="E5" t="n">
-        <v>15019638190.16</v>
+        <v>11757656080.87</v>
       </c>
       <c r="F5" t="n">
-        <v>24730644974.6</v>
+        <v>31033280918.54</v>
       </c>
       <c r="G5" t="n">
-        <v>45864028995.77</v>
+        <v>48593502362.83</v>
       </c>
       <c r="H5" t="n">
-        <v>12087090753.8</v>
+        <v>8707701345.049999</v>
       </c>
       <c r="I5" t="n">
-        <v>24730644974.6</v>
+        <v>31033280918.54</v>
       </c>
       <c r="J5" t="n">
-        <v>2256826686.63</v>
+        <v>2731748480.34</v>
       </c>
       <c r="K5" t="n">
-        <v>33101217492.24</v>
+        <v>39567594762.3</v>
       </c>
       <c r="L5" t="n">
-        <v>45059753462.42</v>
+        <v>44874798628.22</v>
       </c>
       <c r="M5" t="n">
-        <v>35050301944.08</v>
+        <v>42040678218.49</v>
       </c>
       <c r="N5" t="n">
-        <v>1949084451.84</v>
+        <v>2473083456.19</v>
       </c>
       <c r="O5" t="n">
-        <v>33101217492.24</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>39567594762.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>174944256.65</v>
+      </c>
       <c r="Q5" t="n">
-        <v>18448415734.99</v>
+        <v>23424281261.35</v>
       </c>
       <c r="R5" t="n">
-        <v>7400803875</v>
+        <v>7294216875</v>
       </c>
       <c r="S5" t="n">
-        <v>7400803875</v>
+        <v>7294216875</v>
       </c>
       <c r="T5" t="n">
-        <v>39256062851.16</v>
+        <v>35154821919.36</v>
       </c>
       <c r="U5" t="n">
-        <v>14982186213.82</v>
+        <v>8227525622.66</v>
       </c>
       <c r="V5" t="n">
-        <v>583035291.61</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2579073.52</v>
-      </c>
+        <v>23339731.15</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>120502676.88</v>
+        <v>3564107.17</v>
       </c>
       <c r="Y5" t="n">
-        <v>426110625.78</v>
+        <v>525236135.58</v>
       </c>
       <c r="Z5" t="n">
-        <v>179851893.45</v>
+        <v>283733107.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>13672685726.1</v>
+        <v>7391652540.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1714149755.92</v>
+        <v>2084448674.98</v>
       </c>
       <c r="AC5" t="n">
-        <v>11958535970.18</v>
+        <v>5307203865.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>24273876637.34</v>
+        <v>26927296296.7</v>
       </c>
       <c r="AE5" t="n">
-        <v>317808684.84</v>
+        <v>10825386.94</v>
       </c>
       <c r="AF5" t="n">
-        <v>1346952464.06</v>
+        <v>4366003539.97</v>
       </c>
       <c r="AG5" t="n">
-        <v>542676930.71</v>
+        <v>647299805.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>804275533.35</v>
+        <v>3718703734.61</v>
       </c>
       <c r="AI5" t="n">
-        <v>1980502961.29</v>
+        <v>174384897.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16632877235.75</v>
+        <v>15667557383.77</v>
       </c>
       <c r="AK5" t="n">
-        <v>1884331928.68</v>
+        <v>1972767130.13</v>
       </c>
       <c r="AL5" t="n">
-        <v>64040629.95</v>
+        <v>73788729.28</v>
       </c>
       <c r="AM5" t="n">
-        <v>815825787.16</v>
+        <v>864106652.46</v>
       </c>
       <c r="AN5" t="n">
-        <v>13868678889.96</v>
+        <v>12756894871.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>74306364795.24001</v>
+        <v>77195500137.85001</v>
       </c>
       <c r="AP5" t="n">
-        <v>37945397404.1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>324454648.11</v>
-      </c>
+        <v>41560502496.1</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>236049377.05</v>
+        <v>221218439.51</v>
       </c>
       <c r="AS5" t="n">
-        <v>259677060.28</v>
+        <v>320385056.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>824200531.45</v>
+        <v>1632133803.25</v>
       </c>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>824200531.45</v>
+        <v>416867662.27</v>
       </c>
       <c r="AW5" t="n">
-        <v>797864160.84</v>
+        <v>1215266140.98</v>
       </c>
       <c r="AX5" t="n">
-        <v>8412239568.62</v>
+        <v>9239887191.07</v>
       </c>
       <c r="AY5" t="n">
-        <v>2174711358.92</v>
+        <v>2793232058.42</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8370572517.64</v>
+        <v>8534313843.76</v>
       </c>
       <c r="BA5" t="n">
-        <v>6388174268.98</v>
+        <v>6568744342.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1982398248.66</v>
+        <v>1965569500.96</v>
       </c>
       <c r="BC5" t="n">
-        <v>17295888171.65</v>
+        <v>18733510730.62</v>
       </c>
       <c r="BD5" t="n">
-        <v>-10476004078.47</v>
+        <v>-13792337643.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>27771892250.12</v>
+        <v>32525848374.42</v>
       </c>
       <c r="BF5" t="n">
-        <v>1073460119.79</v>
+        <v>707241506.88</v>
       </c>
       <c r="BG5" t="n">
-        <v>54931774.27</v>
+        <v>46402685.29</v>
       </c>
       <c r="BH5" t="n">
-        <v>9386272214.41</v>
+        <v>11155649758.93</v>
       </c>
       <c r="BI5" t="n">
-        <v>17257228141.65</v>
+        <v>20616554423.32</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>36360967391.14</v>
+        <v>35634997641.75</v>
       </c>
       <c r="BL5" t="n">
-        <v>582917064.75</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
+        <v>3739850.11</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1378252249.97</v>
+      </c>
       <c r="BN5" t="n">
-        <v>5768041105.33</v>
+        <v>5533635740.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>68997091.31999999</v>
+        <v>56259409.64</v>
       </c>
       <c r="BP5" t="n">
-        <v>25594444.81</v>
+        <v>7559958</v>
       </c>
       <c r="BQ5" t="n">
-        <v>43402646.51</v>
+        <v>48699451.64</v>
       </c>
       <c r="BR5" t="n">
-        <v>1256015785.72</v>
+        <v>1820249334.4</v>
       </c>
       <c r="BS5" t="n">
-        <v>582917064.75</v>
+        <v>322821726.49</v>
       </c>
       <c r="BT5" t="n">
-        <v>14187336226.97</v>
+        <v>13051800450.54</v>
       </c>
       <c r="BU5" t="n">
-        <v>-524850233.24</v>
+        <v>-545188204.76</v>
       </c>
       <c r="BV5" t="n">
-        <v>14712186460.21</v>
+        <v>13596988655.3</v>
       </c>
       <c r="BW5" t="n">
-        <v>14497660117.05</v>
+        <v>13468238880.3</v>
       </c>
       <c r="BX5" t="n">
-        <v>794623.45</v>
+        <v>574374.3199999999</v>
       </c>
       <c r="BY5" t="n">
-        <v>14496865493.6</v>
+        <v>13467664505.98</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4947556879.94</v>
+        <v>5787029280.41</v>
       </c>
       <c r="CA5" t="n">
-        <v>9549308613.66</v>
+        <v>7680635225.57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7173751227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7173751227</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11662825862.12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32958737174.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>49922575969.84</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14560330043.37</v>
+      </c>
+      <c r="I6" t="n">
+        <v>32958737174.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3029813742.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>41289563850.47</v>
+      </c>
+      <c r="L6" t="n">
+        <v>47836922606.83</v>
+      </c>
+      <c r="M6" t="n">
+        <v>44044448601.35</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2754884750.88</v>
+      </c>
+      <c r="O6" t="n">
+        <v>41289563850.47</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>25114095373.21</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7173751227</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7173751227</v>
+      </c>
+      <c r="T6" t="n">
+        <v>34303420852.14</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9855388569.67</v>
+      </c>
+      <c r="V6" t="n">
+        <v>67593194.84</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>3485618.9</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>431588952.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>335919666</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9016801137.73</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2469442381.37</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6547358756.36</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>24448032282.47</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>19289448.81</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2646024724.39</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>560371361.38</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2085653363.01</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>146291194.79</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>15228510009.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1785211259.28</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>12950281.88</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>684108566.67</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12746239901.23</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>78347869453.49001</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>39339507127.65</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>161405.06</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>208170784.77</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>391732202.93</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2669014967.73</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1351795493.97</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1317219473.76</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6721434703.68</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2592913504.53</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>8330826676.27</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6758556700.15</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1572269976.12</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>18298127222.21</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-14653484871.32</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>32951612093.53</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1010299126.94</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>38048057.46</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>11060443987.31</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>20842820921.82</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>39008362325.84</v>
+      </c>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="n">
+        <v>1101003780.55</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5462871162.14</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>59990700.73</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>9061218.41</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>50929482.32</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1936200126.13</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>369326645.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>13068313858.71</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-776400389.92</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>13844714248.63</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>17010656052.57</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1031653.86</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>17009624398.71</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>5838359951.91</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>11171264446.8</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2981,670 +3128,746 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2556567660.01</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-69107078.09999999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-182701036.16</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8440403579.52</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>-1554692154.69</v>
-      </c>
-      <c r="H2" t="n">
-        <v>13440376824.37</v>
-      </c>
-      <c r="I2" t="n">
-        <v>13826301140.45</v>
-      </c>
-      <c r="J2" t="n">
-        <v>34629481.99</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-420553798.07</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-4739201328.55</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-9239865669.59</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-297549117.15</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-2105440176.05</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-2105440176.05</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>14787848.9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-69107078.09999999</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>8257702543.36</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-1091983361.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-182701036.16</v>
-      </c>
-      <c r="W2" t="n">
-        <v>8440403579.52</v>
-      </c>
-      <c r="X2" t="n">
-        <v>207387715.78</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>139548475.48</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>1777325967.34</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-336992352.47</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>29388630.63</v>
-      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>29388630.63</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1401883005.2</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>152809149.49</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1554692154.69</v>
-      </c>
+        <v>1568084.93</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>4111259814.7</v>
+        <v>4164899744.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>-752847753.38</v>
+        <v>-229442397.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>-43416904.56</v>
+        <v>-34628610.89</v>
       </c>
       <c r="AM2" t="n">
-        <v>794770038.08</v>
+        <v>5009346955.84</v>
       </c>
       <c r="AN2" t="n">
-        <v>2085417.67</v>
+        <v>4661462.92</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1506286304.57</v>
+        <v>-5208822205.57</v>
       </c>
       <c r="AP2" t="n">
-        <v>448618632.84</v>
+        <v>600469372.74</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2474463188.31</v>
+        <v>2101376039.79</v>
       </c>
       <c r="AR2" t="n">
-        <v>325216797.78</v>
+        <v>277655096.32</v>
       </c>
       <c r="AS2" t="n">
-        <v>2149246390.53</v>
+        <v>1823720943.47</v>
       </c>
       <c r="AT2" t="n">
-        <v>-362588705.73</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-53033631.65</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5417965.06</v>
-      </c>
+        <v>-2589855121.54</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>4179646600.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4111259814.7</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-1931912269.69</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-107887566571.79</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-1498055837.16</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-7813679525.52</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-98575831209.11</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>113930738656.18</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2594420072.61</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>111336318583.57</v>
-      </c>
+        <v>3932723020.3</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2220938230.77</v>
+        <v>3685092182.4</v>
       </c>
       <c r="C3" t="n">
-        <v>-26775283.28</v>
+        <v>-389925691.09</v>
       </c>
       <c r="D3" t="n">
-        <v>-118292572.11</v>
+        <v>-3324074902.47</v>
       </c>
       <c r="E3" t="n">
-        <v>1122996754.38</v>
+        <v>2451422629.65</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="G3" t="n">
-        <v>-1611999258.05</v>
+        <v>-1560319895.25</v>
       </c>
       <c r="H3" t="n">
-        <v>13826301140.45</v>
+        <v>16405563975.61</v>
       </c>
       <c r="I3" t="n">
-        <v>16406264443</v>
+        <v>14308375557.08</v>
       </c>
       <c r="J3" t="n">
-        <v>73606595.52</v>
+        <v>435709731.19</v>
       </c>
       <c r="K3" t="n">
-        <v>-2653569898.07</v>
+        <v>1661478687.34</v>
       </c>
       <c r="L3" t="n">
-        <v>-6704816117.56</v>
+        <v>-4598913735.77</v>
       </c>
       <c r="M3" t="n">
-        <v>-4266844484.05</v>
+        <v>118176225.25</v>
       </c>
       <c r="N3" t="n">
-        <v>-367121456.1</v>
+        <v>-382443636.58</v>
       </c>
       <c r="O3" t="n">
-        <v>-1774016879.15</v>
+        <v>-2080591039.93</v>
       </c>
       <c r="P3" t="n">
-        <v>-1774016879.15</v>
+        <v>-2080591039.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>-26775283.28</v>
+        <v>-389925691.09</v>
       </c>
       <c r="R3" t="n">
-        <v>-26775283.28</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>-389925691.09</v>
+      </c>
+      <c r="S3" t="n">
+        <v>40000000</v>
+      </c>
       <c r="T3" t="n">
-        <v>1004704182.27</v>
+        <v>-872652272.8200001</v>
       </c>
       <c r="U3" t="n">
-        <v>-3326536929.81</v>
+        <v>-872652272.8200001</v>
       </c>
       <c r="V3" t="n">
-        <v>-118292572.11</v>
+        <v>-3324074902.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1122996754.38</v>
+        <v>2451422629.65</v>
       </c>
       <c r="X3" t="n">
-        <v>218308730.67</v>
+        <v>1014980345.46</v>
       </c>
       <c r="Y3" t="n">
-        <v>32250304.16</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>5984170.38</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2351168576.74</v>
+      </c>
       <c r="AA3" t="n">
-        <v>1894458595.27</v>
+        <v>2275669396.81</v>
       </c>
       <c r="AB3" t="n">
-        <v>2208204693.05</v>
+        <v>2360838580.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>-313746097.78</v>
+        <v>-85169183.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>-484608440.05</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>10915560.74</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>197209205.34</v>
+      </c>
       <c r="AF3" t="n">
-        <v>-484608440.05</v>
+        <v>-186293644.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1223791728.71</v>
+        <v>-1284713782.47</v>
       </c>
       <c r="AH3" t="n">
-        <v>388207529.34</v>
+        <v>275606112.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1611999258.05</v>
+        <v>-1560319895.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3837120750.28</v>
+        <v>5118247580</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1177597892.99</v>
+        <v>958787547.61</v>
       </c>
       <c r="AL3" t="n">
-        <v>-39049838.86</v>
+        <v>15856652.24</v>
       </c>
       <c r="AM3" t="n">
-        <v>-2723752787.55</v>
+        <v>1241300126.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>15175160.04</v>
+        <v>3535831.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>1570029573.38</v>
+        <v>-301905061.84</v>
       </c>
       <c r="AP3" t="n">
-        <v>525528712.52</v>
+        <v>136437777.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2464068269.76</v>
+        <v>2310098291.24</v>
       </c>
       <c r="AR3" t="n">
-        <v>300380484.03</v>
+        <v>322442487.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>2163687785.73</v>
+        <v>1987655803.29</v>
       </c>
       <c r="AT3" t="n">
-        <v>-509688625.21</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-181172962.97</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-4914925.5</v>
-      </c>
+        <v>-265374188.2</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>4452687889.82</v>
+        <v>4240660476.68</v>
       </c>
       <c r="AX3" t="n">
-        <v>3832937488.82</v>
+        <v>5245412077.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>-2010022617.66</v>
+        <v>-1876162080.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-105410772043.2</v>
+        <v>-111212597874.02</v>
       </c>
       <c r="BA3" t="n">
-        <v>-2428385605.34</v>
+        <v>-1300453042</v>
       </c>
       <c r="BB3" t="n">
-        <v>-7855678863.64</v>
+        <v>-7614030217.73</v>
       </c>
       <c r="BC3" t="n">
-        <v>-95126707574.22</v>
+        <v>-102298114614.29</v>
       </c>
       <c r="BD3" t="n">
-        <v>111253732149.68</v>
+        <v>118334172031.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>2927385563.52</v>
+        <v>3158008325.55</v>
       </c>
       <c r="BF3" t="n">
-        <v>108326346586.16</v>
+        <v>115176163706.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3685092182.4</v>
+        <v>2220938230.77</v>
       </c>
       <c r="C4" t="n">
-        <v>-389925691.09</v>
+        <v>-26775283.28</v>
       </c>
       <c r="D4" t="n">
-        <v>-3324074902.47</v>
+        <v>-118292572.11</v>
       </c>
       <c r="E4" t="n">
-        <v>2451422629.65</v>
+        <v>1122996754.38</v>
       </c>
       <c r="F4" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1560319895.25</v>
+        <v>-1611999258.05</v>
       </c>
       <c r="H4" t="n">
-        <v>16405563975.61</v>
+        <v>13826301140.45</v>
       </c>
       <c r="I4" t="n">
-        <v>14308375557.08</v>
+        <v>16406264443</v>
       </c>
       <c r="J4" t="n">
-        <v>435709731.19</v>
+        <v>73606595.52</v>
       </c>
       <c r="K4" t="n">
-        <v>1661478687.34</v>
+        <v>-2653569898.07</v>
       </c>
       <c r="L4" t="n">
-        <v>-4598913735.77</v>
+        <v>-6704816117.56</v>
       </c>
       <c r="M4" t="n">
-        <v>118176225.25</v>
+        <v>-4266844484.05</v>
       </c>
       <c r="N4" t="n">
-        <v>-382443636.58</v>
+        <v>-367121456.1</v>
       </c>
       <c r="O4" t="n">
-        <v>-2080591039.93</v>
+        <v>-1774016879.15</v>
       </c>
       <c r="P4" t="n">
-        <v>-2080591039.93</v>
+        <v>-1774016879.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>-389925691.09</v>
+        <v>-26775283.28</v>
       </c>
       <c r="R4" t="n">
-        <v>-389925691.09</v>
-      </c>
-      <c r="S4" t="n">
-        <v>40000000</v>
-      </c>
+        <v>-26775283.28</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>-872652272.8200001</v>
+        <v>1004704182.27</v>
       </c>
       <c r="U4" t="n">
-        <v>-872652272.8200001</v>
+        <v>-3326536929.81</v>
       </c>
       <c r="V4" t="n">
-        <v>-3324074902.47</v>
+        <v>-118292572.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2451422629.65</v>
+        <v>1122996754.38</v>
       </c>
       <c r="X4" t="n">
-        <v>1014980345.46</v>
+        <v>218308730.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>5984170.38</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2351168576.74</v>
-      </c>
+        <v>32250304.16</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>2275669396.81</v>
+        <v>1894458595.27</v>
       </c>
       <c r="AB4" t="n">
-        <v>2360838580.11</v>
+        <v>2208204693.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>-85169183.3</v>
+        <v>-313746097.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>10915560.74</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>197209205.34</v>
-      </c>
+        <v>-484608440.05</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-186293644.6</v>
+        <v>-484608440.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1284713782.47</v>
+        <v>-1223791728.71</v>
       </c>
       <c r="AH4" t="n">
-        <v>275606112.78</v>
+        <v>388207529.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1560319895.25</v>
+        <v>-1611999258.05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5118247580</v>
+        <v>3837120750.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>958787547.61</v>
+        <v>-1177597892.99</v>
       </c>
       <c r="AL4" t="n">
-        <v>15856652.24</v>
+        <v>-39049838.86</v>
       </c>
       <c r="AM4" t="n">
-        <v>1241300126.06</v>
+        <v>-2723752787.55</v>
       </c>
       <c r="AN4" t="n">
-        <v>3535831.15</v>
+        <v>15175160.04</v>
       </c>
       <c r="AO4" t="n">
-        <v>-301905061.84</v>
+        <v>1570029573.38</v>
       </c>
       <c r="AP4" t="n">
-        <v>136437777.9</v>
+        <v>525528712.52</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2310098291.24</v>
+        <v>2464068269.76</v>
       </c>
       <c r="AR4" t="n">
-        <v>322442487.95</v>
+        <v>300380484.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1987655803.29</v>
+        <v>2163687785.73</v>
       </c>
       <c r="AT4" t="n">
-        <v>-265374188.2</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
+        <v>-509688625.21</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-181172962.97</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-4914925.5</v>
+      </c>
       <c r="AW4" t="n">
-        <v>4240660476.68</v>
+        <v>4452687889.82</v>
       </c>
       <c r="AX4" t="n">
-        <v>5245412077.65</v>
+        <v>3832937488.82</v>
       </c>
       <c r="AY4" t="n">
-        <v>-1876162080.01</v>
+        <v>-2010022617.66</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-111212597874.02</v>
+        <v>-105410772043.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1300453042</v>
+        <v>-2428385605.34</v>
       </c>
       <c r="BB4" t="n">
-        <v>-7614030217.73</v>
+        <v>-7855678863.64</v>
       </c>
       <c r="BC4" t="n">
-        <v>-102298114614.29</v>
+        <v>-95126707574.22</v>
       </c>
       <c r="BD4" t="n">
-        <v>118334172031.68</v>
+        <v>111253732149.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>3158008325.55</v>
+        <v>2927385563.52</v>
       </c>
       <c r="BF4" t="n">
-        <v>115176163706.13</v>
+        <v>108326346586.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2717664362.34</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>2556567660.01</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-69107078.09999999</v>
+      </c>
       <c r="D5" t="n">
-        <v>-8276128799.57</v>
+        <v>-182701036.16</v>
       </c>
       <c r="E5" t="n">
-        <v>8802968327.41</v>
+        <v>8440403579.52</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-1446897297.87</v>
+        <v>-1554692154.69</v>
       </c>
       <c r="H5" t="n">
-        <v>14211362240.62</v>
+        <v>13440376824.37</v>
       </c>
       <c r="I5" t="n">
-        <v>11294410767.98</v>
+        <v>13826301140.45</v>
       </c>
       <c r="J5" t="n">
-        <v>-111791711.23</v>
+        <v>34629481.99</v>
       </c>
       <c r="K5" t="n">
-        <v>3028743183.87</v>
+        <v>-420553798.07</v>
       </c>
       <c r="L5" t="n">
-        <v>-1608606792.71</v>
+        <v>-4739201328.55</v>
       </c>
       <c r="M5" t="n">
-        <v>-768675543.42</v>
+        <v>-9239865669.59</v>
       </c>
       <c r="N5" t="n">
-        <v>-337995954.45</v>
+        <v>-297549117.15</v>
       </c>
       <c r="O5" t="n">
-        <v>-888431094.85</v>
+        <v>-2105440176.05</v>
       </c>
       <c r="P5" t="n">
-        <v>-888431094.85</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>-2105440176.05</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14787848.9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-69107078.09999999</v>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>526839527.84</v>
+        <v>8257702543.36</v>
       </c>
       <c r="U5" t="n">
-        <v>526839527.84</v>
+        <v>-1091983361.01</v>
       </c>
       <c r="V5" t="n">
-        <v>-8276128799.57</v>
+        <v>-182701036.16</v>
       </c>
       <c r="W5" t="n">
-        <v>8802968327.41</v>
+        <v>8440403579.52</v>
       </c>
       <c r="X5" t="n">
-        <v>472788316.37</v>
+        <v>207387715.78</v>
       </c>
       <c r="Y5" t="n">
-        <v>13925000</v>
+        <v>139548475.48</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>1999374145.42</v>
+        <v>1777325967.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>-128994516.8</v>
+        <v>-336992352.47</v>
       </c>
       <c r="AD5" t="n">
-        <v>-189245561.2</v>
+        <v>29388630.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>1568084.93</v>
+        <v>29388630.63</v>
       </c>
       <c r="AF5" t="n">
-        <v>-190813646.13</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1222270751.05</v>
+        <v>-1401883005.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>224626546.82</v>
+        <v>152809149.49</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1446897297.87</v>
+        <v>-1554692154.69</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4164899744.5</v>
+        <v>4111259814.7</v>
       </c>
       <c r="AK5" t="n">
-        <v>-229442397.7</v>
+        <v>-752847753.38</v>
       </c>
       <c r="AL5" t="n">
-        <v>-34628610.89</v>
+        <v>-43416904.56</v>
       </c>
       <c r="AM5" t="n">
-        <v>5009346955.84</v>
+        <v>794770038.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>4661462.92</v>
+        <v>2085417.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>-5208822205.57</v>
+        <v>-1506286304.57</v>
       </c>
       <c r="AP5" t="n">
-        <v>600469372.74</v>
+        <v>448618632.84</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2101376039.79</v>
+        <v>2474463188.31</v>
       </c>
       <c r="AR5" t="n">
-        <v>277655096.32</v>
+        <v>325216797.78</v>
       </c>
       <c r="AS5" t="n">
-        <v>1823720943.47</v>
+        <v>2149246390.53</v>
       </c>
       <c r="AT5" t="n">
-        <v>-2589855121.54</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
+        <v>-362588705.73</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-53033631.65</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5417965.06</v>
+      </c>
       <c r="AW5" t="n">
-        <v>3932723020.3</v>
+        <v>4179646600.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4164561660.21</v>
+        <v>4111259814.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>-1525977922.33</v>
+        <v>-1931912269.69</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-126580034862.51</v>
+        <v>-107887566571.79</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1246100584.56</v>
+        <v>-1498055837.16</v>
       </c>
       <c r="BB5" t="n">
-        <v>-6934340949.35</v>
+        <v>-7813679525.52</v>
       </c>
       <c r="BC5" t="n">
-        <v>-118399593328.6</v>
+        <v>-98575831209.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>132270574445.05</v>
+        <v>113930738656.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>2393802806.76</v>
+        <v>2594420072.61</v>
       </c>
       <c r="BF5" t="n">
-        <v>129876771638.29</v>
+        <v>111336318583.57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1432987224.71</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-479283332.72</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-4603619728.83</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4155754976.87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>72838814</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1652518918.57</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16889324770.55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13440376824.37</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-63166966.18</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3512114912.36</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-4399849653.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-13954643.77</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-164738654.08</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-2075499846.51</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-2075499846.51</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-406444518.72</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-479283332.72</v>
+      </c>
+      <c r="S6" t="n">
+        <v>72838814</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-447864751.96</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-447864751.96</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-4603619728.83</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4155754976.87</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4826458422.76</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>86899805.69</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>5058378314.33</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5997879111.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-939500797.17</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1223132611.97</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1223132611.97</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-1541952309.23</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>110566609.34</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1652518918.57</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>3085506143.28</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-2163840802.38</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-98732185960.39999</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-1463220215.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-7871437556.54</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-89397528188.85001</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>103981532906.06</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2444257189.89</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>101537275716.17</v>
       </c>
     </row>
   </sheetData>
@@ -3658,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FM2"/>
+  <dimension ref="A1:FF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3839,670 +4062,635 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>forwardPE</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>fiveYearAvgDividendYield</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>forwardPE</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>forwardEps</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>pegRatio</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>earningsQuarterlyGrowth</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>forwardEps</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>pegRatio</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>targetHighPrice</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>targetLowPrice</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>targetMeanPrice</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>targetMedianPrice</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>targetHighPrice</t>
+          <t>numberOfAnalystOpinions</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>targetLowPrice</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>targetMeanPrice</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>targetMedianPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>recommendationMean</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>numberOfAnalystOpinions</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DK1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DL1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DM1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DN1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DO1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DP1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="DQ1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DR1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>messageBoardId</t>
         </is>
       </c>
       <c r="DS1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>exchangeTimezoneName</t>
         </is>
       </c>
       <c r="DT1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>exchangeTimezoneShortName</t>
         </is>
       </c>
       <c r="DU1" t="inlineStr">
         <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
       <c r="FD1" t="inlineStr">
         <is>
-          <t>messageBoardId</t>
+          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="FE1" t="inlineStr">
         <is>
-          <t>exchangeTimezoneName</t>
+          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="FF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="FK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FM1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4524,10 +4712,8 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100029</t>
-        </is>
+      <c r="D2" t="n">
+        <v>100029</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4589,7 +4775,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Xiang  Gao', 'age': 53, 'title': 'Chief Digital Officer, President &amp; Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 1650783, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaoyan  Li', 'age': 48, 'title': 'Chief Financial Officer', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shichu  Li', 'age': 55, 'title': 'VP, Deputy GM, General Counsel, Chief Compliance Officer &amp; Secretary', 'yearBorn': 1970, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fei  He', 'age': 42, 'title': 'Deputy General Manager', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dupeng  Wang', 'age': 53, 'title': 'Vice President', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jian  Wang', 'age': 53, 'title': 'Deputy General Manager', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Xiang  Gao', 'age': 53, 'title': 'Chief Digital Officer, President &amp; Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 1650950, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaoyan  Li', 'age': 48, 'title': 'Chief Financial Officer', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shichu  Li', 'age': 55, 'title': 'VP, Deputy GM, General Counsel, Chief Compliance Officer &amp; Secretary', 'yearBorn': 1970, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fei  He', 'age': 42, 'title': 'Deputy General Manager', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dupeng  Wang', 'age': 53, 'title': 'Vice President', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jian  Wang', 'age': 53, 'title': 'Deputy General Manager', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4608,7 +4794,7 @@
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="X2" t="n">
         <v>1767139200</v>
@@ -4625,475 +4811,452 @@
         <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.775</v>
+        <v>4.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.78</v>
+        <v>4.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.7</v>
+        <v>4.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.88</v>
+        <v>4.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.775</v>
+        <v>4.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.78</v>
+        <v>4.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.7</v>
+        <v>4.06</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.88</v>
+        <v>4.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.35</v>
+        <v>1.146</v>
       </c>
       <c r="AK2" t="n">
-        <v>7.34</v>
+        <v>6.276923</v>
       </c>
       <c r="AL2" t="n">
+        <v>7.614796</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>11641000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11641000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5639101</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6304168</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6304168</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>29268903936</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>29268905006</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.3094412</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.9302</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.05555</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.07058824</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="BH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>30105368576</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2760029047</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2016281000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.24589</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>7173751227</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>6.739908</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.6053495</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>4058247936</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.53579897</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.051546335</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="CE2" t="n">
         <v>1780358400</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.52959996</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.154</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.587302</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.922159000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6922000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6922000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5275221</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5977053</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5977053</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="CG2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>6.5561047</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>3.228867</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>5.146316</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>5.6464667</v>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CM2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>14537389056</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>3631491584</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>11053612032</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>94586314752</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>24.807</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>13.199</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.09866999999999999</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>5451975168</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1220697984</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>2644516608</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.093</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.05764</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.03839</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0598.HK</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
         <v>0</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>1781770086</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>finmb_6700882</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DW2" t="b">
         <v>0</v>
       </c>
-      <c r="BA2" t="n">
-        <v>34290532352</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>35510068573</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="BF2" t="n">
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>SINOTRANS</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Sinotrans Limited</t>
+        </is>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1045099800000</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.17000008</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>4.06 - 4.25</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>5639101</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.06806283</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>3.82 - 5.51</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-1.4300003</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.2595282</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>5.1546335</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1777363800</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1777363800</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1777363800</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1748926800</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1748926800</v>
+      </c>
+      <c r="ER2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ES2" t="n">
         <v>0.65</v>
       </c>
-      <c r="BG2" t="n">
-        <v>0.36253163</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5.0354</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>5.0624</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.06282723</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="BM2" t="b">
+      <c r="ET2" t="n">
+        <v>0.53579897</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>9.383623999999999</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-0.8502002</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>-0.1724474</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>-0.9755502</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>-0.19296618</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FC2" t="b">
         <v>0</v>
       </c>
-      <c r="BN2" t="n">
-        <v>33620506624</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.04291</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2760029047</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>2016281000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.24589</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.31288</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>7173751227</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>6.7392273</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.70928013</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>4058247936</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0.5357448</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>9.257999999999999</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0.29581153</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.1754</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1780358400</v>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CL2" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>6.5623364</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>3.2319362</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>5.151208</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>5.651834</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>2.57143</v>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="CS2" t="n">
-        <v>6</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>14537389056</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>2.026</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>3631491584</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>11053612032</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>94586314752</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>24.807</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>13.199</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.01615</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0.09866999999999999</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>5451975168</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1220697984</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>2644516608</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.093</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.05764</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.03839</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>0598.HK</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.0050001144</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>4.7 - 4.88</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>5275221</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1.0900002</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.295393</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>3.69 - 5.51</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.73</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.13248639</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>29.581154</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1777363800</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1777363800</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1777363800</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1748926800</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1748926800</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.5357448</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.4348</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>10.993561</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.2553997</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-0.050720837</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.28239965</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-0.055783752</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>2.6 - Hold</t>
-        </is>
-      </c>
-      <c r="EV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1045099800000</v>
-      </c>
-      <c r="EX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>SINOTRANS</t>
-        </is>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>Sinotrans Limited</t>
-        </is>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': '0598.HK announced a cash dividend of HKD 0.175 with an ex-date of Jun. 2, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1780329600000, 'amount': '0.175'}}]</t>
-        </is>
-      </c>
-      <c r="FB2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>finmb_6700882</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="FG2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="FI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="FK2" t="n">
-        <v>0.10471444</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="FM2" t="inlineStr"/>
+      <c r="FD2" t="n">
+        <v>-4.000002</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="FF2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
